--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22941-2024 artfynd.xlsx
+++ b/artfynd/A 22941-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136545482</v>
       </c>
       <c r="B2" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136545989</v>
       </c>
       <c r="B3" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
